--- a/sources/pdc.xlsx
+++ b/sources/pdc.xlsx
@@ -924,7 +924,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Design Grade sulphur grade based on Primero circuit modelling</t>
+          <t>Design Grade sulphur grade based on EPC circuit modelling</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Increased to 90% from 84% (Source 44) as per meeting with NSR</t>
+          <t>Increased to 90% from 84% (Source 44) as per meeting with Owner</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -9969,7 +9969,7 @@
     <row r="78">
       <c r="L78" t="inlineStr">
         <is>
-          <t>&amp; Primero 22/01/25</t>
+          <t>&amp; EPC 22/01/25</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -11989,7 +11989,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>As per KCGM-P3-EPC-COR-602</t>
+          <t>As per P3-EPC-COR-602</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -12294,12 +12294,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-602</t>
+          <t>P3-EPC-COR-602</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -12363,7 +12363,7 @@
     <row r="18">
       <c r="L18" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-602</t>
+          <t>P3-EPC-COR-602</t>
         </is>
       </c>
     </row>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -13900,7 +13900,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -14083,7 +14083,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -14631,7 +14631,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -14935,7 +14935,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -14982,7 +14982,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -15034,7 +15034,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -15575,7 +15575,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -16012,7 +16012,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -16378,7 +16378,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -16682,7 +16682,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -16969,7 +16969,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -17664,7 +17664,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17886,7 +17886,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -17999,7 +17999,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -18390,7 +18390,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -18847,7 +18847,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -19740,7 +19740,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -19777,7 +19777,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -19873,7 +19873,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -19952,7 +19952,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -19989,7 +19989,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -20117,7 +20117,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -20149,7 +20149,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20437,7 +20437,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -20607,7 +20607,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -20681,7 +20681,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -20777,7 +20777,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -20821,7 +20821,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -20890,7 +20890,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -20922,7 +20922,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -21153,7 +21153,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -21222,7 +21222,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -21466,7 +21466,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -21503,7 +21503,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -21707,7 +21707,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -21766,7 +21766,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -22160,7 +22160,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -22197,7 +22197,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -22593,7 +22593,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -22758,7 +22758,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -22868,7 +22868,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -22937,7 +22937,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -23085,7 +23085,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -23493,7 +23493,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -23562,7 +23562,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5 BVs of Pregnant Eluate required by NSR (Source 8)</t>
+          <t>5 BVs of Pregnant Eluate required by Owner (Source 8)</t>
         </is>
       </c>
     </row>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -24245,7 +24245,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -24309,7 +24309,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>5 BVs of Pregnant Eluate required by NSR (Source 15)</t>
+          <t>5 BVs of Pregnant Eluate required by Owner (Source 15)</t>
         </is>
       </c>
     </row>
@@ -24358,7 +24358,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -24628,7 +24628,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -24768,7 +24768,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Total of 5 BVs of Lean Eluate required by NSR (Source 8)</t>
+          <t>Total of 5 BVs of Lean Eluate required by Owner (Source 8)</t>
         </is>
       </c>
     </row>
@@ -25192,7 +25192,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -25334,7 +25334,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -26359,7 +26359,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -26504,7 +26504,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -26610,7 +26610,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -26642,7 +26642,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -26674,7 +26674,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -26822,7 +26822,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -26896,7 +26896,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -27103,7 +27103,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -27203,7 +27203,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -27240,7 +27240,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -27277,7 +27277,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -27390,7 +27390,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -27427,7 +27427,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -27469,7 +27469,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -27506,7 +27506,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -27789,7 +27789,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -27826,7 +27826,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -27890,7 +27890,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -27991,7 +27991,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -28045,7 +28045,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -28087,7 +28087,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -28193,7 +28193,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -28269,7 +28269,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -28646,7 +28646,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -28734,7 +28734,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -28845,7 +28845,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -28882,7 +28882,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -28958,7 +28958,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -28995,7 +28995,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -29032,7 +29032,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -29145,7 +29145,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -29182,7 +29182,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -29214,7 +29214,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -29295,7 +29295,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -29376,7 +29376,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -29413,7 +29413,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -29450,7 +29450,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -29487,7 +29487,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -29541,7 +29541,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Fimiston ERP Commissioning Report</t>
+          <t>FIM ERP Commissioning Report</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -29573,7 +29573,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -29639,7 +29639,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -29676,7 +29676,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -30055,7 +30055,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -30215,7 +30215,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -30252,7 +30252,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -30434,7 +30434,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -30503,7 +30503,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -30599,7 +30599,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -30673,7 +30673,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -30705,7 +30705,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -30737,7 +30737,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -30774,7 +30774,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -30828,7 +30828,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -30860,7 +30860,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -30892,7 +30892,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -31283,7 +31283,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -31448,7 +31448,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -31687,7 +31687,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -31812,7 +31812,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -32850,7 +32850,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -32887,7 +32887,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -32931,7 +32931,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -32968,7 +32968,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -33037,7 +33037,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -33096,7 +33096,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -33123,22 +33123,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gidji Decant &amp; FIM I Decant</t>
+          <t>offsite roaster Decant &amp; FIM I Decant</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gidji Decant &amp; FIM I Decant</t>
+          <t>offsite roaster Decant &amp; FIM I Decant</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gidji Decant &amp; FIM I Decant</t>
+          <t>offsite roaster Decant &amp; FIM I Decant</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Gidji Decant &amp; FIM I Decant</t>
+          <t>offsite roaster Decant &amp; FIM I Decant</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -33148,7 +33148,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -33257,7 +33257,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -33405,7 +33405,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -33452,7 +33452,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -33499,7 +33499,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -33573,7 +33573,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -33600,7 +33600,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -33679,7 +33679,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -33938,7 +33938,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -34037,7 +34037,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -34089,7 +34089,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -34141,7 +34141,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -34193,7 +34193,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -34240,7 +34240,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -34400,7 +34400,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -35001,7 +35001,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -35100,7 +35100,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -35189,7 +35189,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -35236,7 +35236,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -35387,7 +35387,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -35543,7 +35543,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -35602,7 +35602,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -35654,7 +35654,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -35706,7 +35706,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -35758,7 +35758,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -36647,7 +36647,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -36740,7 +36740,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -36834,7 +36834,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -36989,7 +36989,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -37041,7 +37041,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -37093,7 +37093,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -37187,7 +37187,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -37244,7 +37244,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -37350,7 +37350,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -37402,7 +37402,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -37506,7 +37506,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -38274,7 +38274,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -38326,7 +38326,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -38457,7 +38457,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -38528,7 +38528,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -38580,7 +38580,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -38627,7 +38627,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -38731,7 +38731,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -38820,7 +38820,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -39030,7 +39030,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -39386,7 +39386,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -39739,7 +39739,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -40102,7 +40102,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -40149,7 +40149,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -40201,7 +40201,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -40253,7 +40253,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -40337,7 +40337,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -40460,7 +40460,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -40507,7 +40507,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -40564,7 +40564,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -40670,7 +40670,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -40722,7 +40722,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -40774,7 +40774,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -40833,7 +40833,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -40885,7 +40885,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -40937,7 +40937,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -41465,7 +41465,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -41621,7 +41621,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -41767,7 +41767,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -41821,7 +41821,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -41892,7 +41892,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -41981,7 +41981,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -42075,7 +42075,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -42240,7 +42240,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -42333,7 +42333,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -42385,7 +42385,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -42531,7 +42531,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -42630,7 +42630,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -42719,7 +42719,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -42766,7 +42766,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -42845,7 +42845,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -43075,7 +43075,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -43176,7 +43176,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -43297,7 +43297,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -43349,7 +43349,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -43396,7 +43396,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -43485,7 +43485,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -43589,7 +43589,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -43641,7 +43641,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -43700,7 +43700,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -43757,7 +43757,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -43814,7 +43814,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -43824,7 +43824,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Dosed to six tanks. Total of 21.50 kg/t as per NSR provided data.</t>
+          <t>Dosed to six tanks. Total of 21.50 kg/t as per Owner provided data.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -43955,7 +43955,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -44096,7 +44096,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -44148,7 +44148,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -44212,7 +44212,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -44311,7 +44311,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -44405,7 +44405,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -44504,7 +44504,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -45240,7 +45240,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -45292,7 +45292,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -45386,7 +45386,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -45480,7 +45480,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -45507,7 +45507,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>NSR Supplied Package</t>
+          <t>Owner Supplied Package</t>
         </is>
       </c>
     </row>
@@ -45585,7 +45585,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>NSR Supplied Package</t>
+          <t>Owner Supplied Package</t>
         </is>
       </c>
     </row>
@@ -45715,7 +45715,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -45798,7 +45798,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -45820,7 +45820,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>NSR Supplied Package</t>
+          <t>Owner Supplied Package</t>
         </is>
       </c>
     </row>
@@ -45847,7 +45847,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -45884,7 +45884,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -45968,7 +45968,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -46067,7 +46067,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -46156,7 +46156,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -46203,7 +46203,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -46255,7 +46255,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -46307,7 +46307,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -46366,7 +46366,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -46455,7 +46455,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -46551,7 +46551,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -46702,7 +46702,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -46783,7 +46783,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -46815,7 +46815,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -46874,7 +46874,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -46906,7 +46906,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -46943,7 +46943,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -46980,7 +46980,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -47024,7 +47024,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -47488,7 +47488,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -47520,7 +47520,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -47579,7 +47579,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -47650,7 +47650,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -47815,7 +47815,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -47898,7 +47898,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -47935,7 +47935,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -47967,7 +47967,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -48026,7 +48026,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -48058,7 +48058,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -48095,7 +48095,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -48132,7 +48132,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -48176,7 +48176,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -48240,7 +48240,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -48551,7 +48551,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -48588,7 +48588,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -48652,7 +48652,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -48689,7 +48689,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -48726,7 +48726,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -48787,7 +48787,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -48839,7 +48839,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -48886,7 +48886,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -48938,7 +48938,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -48990,7 +48990,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -49037,7 +49037,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -49141,7 +49141,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -49193,7 +49193,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -49245,7 +49245,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -49423,7 +49423,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -49482,7 +49482,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -49534,7 +49534,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -49581,7 +49581,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -49633,7 +49633,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -49685,7 +49685,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -49732,7 +49732,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -49784,7 +49784,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -49836,7 +49836,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -49888,7 +49888,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -50066,7 +50066,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -50125,7 +50125,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -50177,7 +50177,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -50229,7 +50229,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -50276,7 +50276,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -50328,7 +50328,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -50380,7 +50380,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -50684,7 +50684,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -50736,7 +50736,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -51131,7 +51131,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -51457,7 +51457,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -51499,7 +51499,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -51590,7 +51590,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -51686,7 +51686,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -51770,7 +51770,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -51812,7 +51812,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -51854,7 +51854,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -51896,7 +51896,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -51938,7 +51938,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -52046,7 +52046,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -52083,7 +52083,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -52125,7 +52125,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -52167,7 +52167,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -52209,7 +52209,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -52335,7 +52335,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -52377,7 +52377,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -52419,7 +52419,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -52461,7 +52461,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -52503,7 +52503,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -52596,7 +52596,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -52638,7 +52638,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -52685,7 +52685,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>As per source 82, NSR confirm and accept they won't achieve the</t>
+          <t>As per source 82, Owner confirm and accept they won't achieve the</t>
         </is>
       </c>
     </row>
@@ -52723,7 +52723,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LTD</t>
+          <t>OWNER</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr"/>
@@ -52736,7 +52736,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -52782,7 +52782,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KCGM Growth Project - Process Plant - Site Specific Information</t>
+          <t>Growth Project - Process Plant - Site Specific Information</t>
         </is>
       </c>
     </row>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.7.1 - OMC Report 7555 - KCGM PDC Data Summary Rev 0, March 2022</t>
+          <t>4.7.1 - Consultant Report 7555 - Owner PDC Data Summary Rev 0, March 2022</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -52811,7 +52811,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.6.1 - KCGM Growth Mass Balance_Nominal Case Report_Rev C</t>
+          <t>4.6.1 - Growth Mass Balance_Nominal Case Report_Rev C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -52828,12 +52828,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>"KCGM Comminution Plant Data_B.xlsx"</t>
+          <t>"Owner Comminution Plant Data_B.xlsx"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Benchmarking from Fimiston pebble crushing circuit.</t>
+          <t>Benchmarking from FIM pebble crushing circuit.</t>
         </is>
       </c>
     </row>
@@ -52850,7 +52850,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Q12375 - Primero Gravity Circuit Rev1</t>
+          <t>Q12375 - EPC Gravity Circuit Rev1</t>
         </is>
       </c>
     </row>
@@ -52879,12 +52879,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.7.3 - OMC Report 7555 KCGM PDC PSD Addendum Rev 1</t>
+          <t>4.7.3 - Consultant Report 7555 Owner PDC PSD Addendum Rev 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KCGM - Process Design Criteria Summary - PSD Addendum Report No. 7555 Rev 1 March 2022</t>
+          <t>Process Design Criteria Summary - PSD Addendum Report No. 7555 Rev 1 March 2022</t>
         </is>
       </c>
     </row>
@@ -52901,7 +52901,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.1.12g - BOD Alignment Template - Reagents and Services - Rev C NSR confirmation that regrind mill ball size will be 25 mm (cell F15).</t>
+          <t>5.1.12g - BOD Alignment Template - Reagents and Services - Rev C Owner confirmation that regrind mill ball size will be 25 mm (cell F15).</t>
         </is>
       </c>
     </row>
@@ -52913,7 +52913,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Primero Calculation 23517-CAL-PR-002</t>
+          <t>EPC Calculation CAL-PR-002</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -52930,12 +52930,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KCGM Growth Project ECI Outcome Letter - Primero</t>
+          <t>Growth Project ECI Outcome Letter - EPC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KCGM Growth Project - Process Plant - Formal Agreement for Engineering, Procurement and Construction: Early Contractor Involvement (Value Engineering Phase). 03/08/2022</t>
+          <t>Growth Project - Process Plant - Formal Agreement for Engineering, Procurement and Construction: Early Contractor Involvement (Value Engineering Phase). 03/08/2022</t>
         </is>
       </c>
     </row>
@@ -52952,7 +52952,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5 R. e1 v.1 ie2 wb - BOD Alignment Template -13 Grinding - Rev C - Primero (220609)_NSR</t>
+          <t>5 R. e1 v.1 ie2 wb - BOD Alignment Template -13 Grinding - Rev C - EPC (220609)_Owner</t>
         </is>
       </c>
     </row>
@@ -52964,12 +52964,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KCGM Process Design Criteria - VEP Phase (Stage 1)_I</t>
+          <t>Owner Process Design Criteria - VEP Phase (Stage 1)_I</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KCGM - Growth Project - Process Design Criteria Rev I. 20/09/2022</t>
+          <t>Growth Project - Process Design Criteria Rev I. 20/09/2022</t>
         </is>
       </c>
     </row>
@@ -52981,7 +52981,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cleaner Option 2- KCGM Case 2 Scav Con to Cleaner</t>
+          <t>Cleaner Option 2- Owner Case 2 Scav Con to Cleaner</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -52998,7 +52998,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cleaner Scavenger - KCGM Case 2 Scav to Cleaner</t>
+          <t>Cleaner Scavenger - Owner Case 2 Scav to Cleaner</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -53015,7 +53015,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KCGM GP Process Design Criteria - Reliance Information S1 Rev K, 25/01/2023</t>
+          <t>Owner GP Process Design Criteria - Reliance Information S1 Rev K, 25/01/2023</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -53032,7 +53032,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VEP Outcome Letters - Primero, 09/02/23 and 020523</t>
+          <t>VEP Outcome Letters - EPC, 09/02/23 and 020523</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -53049,12 +53049,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OMC Report 7653 - KCGM Value Engineering Update</t>
+          <t>Consultant Report 7653 - Owner Value Engineering Update</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Grinding circuit modelling for KCGM by Orway Mineral Consultants, 160223</t>
+          <t>Grinding circuit modelling for Owner by Orway Mineral Consultants, 160223</t>
         </is>
       </c>
     </row>
@@ -53066,12 +53066,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Process Design Workshop Meeting Minutes 170223, 23517-MOM-PM-SFP002</t>
+          <t>Process Design Workshop Meeting Minutes 170223, MOM-PM-SFP002</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Workshop between the Client and Primero</t>
+          <t>Workshop between the Client and EPC</t>
         </is>
       </c>
     </row>
@@ -53088,7 +53088,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Simulations from Vendor, 22/02/24 KCGM Expansion Project - Jameson Cell Quote OTJ-2220 7532.3</t>
+          <t>Simulations from Vendor, 22/02/24 Owner Expansion Project - Jameson Cell Quote OTJ-2220 7532.3</t>
         </is>
       </c>
     </row>
@@ -53156,7 +53156,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Emails with Vendor, 14/03/23. Ag and Cu Assays from site, provided by NSR (23/03/23)</t>
+          <t>Emails with Vendor, 14/03/23. Ag and Cu Assays from site, provided by Owner (23/03/23)</t>
         </is>
       </c>
     </row>
@@ -53202,7 +53202,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Direction from Primero Mechanical Engineers re: COS</t>
+          <t>Direction from EPC Mechanical Engineers re: COS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -53253,7 +53253,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Primero Calculation</t>
+          <t>EPC Calculation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -53309,7 +53309,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Scope of Works between NSR and Primero: 2000-F00-SOW-CO-20001 &amp; 2000-F00- SOW-CO-20002_0</t>
+          <t>Scope of Works between Owner and EPC: 2000-F00-SOW-CO-20001 &amp; 2000-F00- SOW-CO-20002_0</t>
         </is>
       </c>
     </row>
@@ -53321,12 +53321,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Outstanding Process Inputs from NSR</t>
+          <t>Outstanding Process Inputs from Owner</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Outstanding Process Inputs 210623 (version 1) Additional (003) (002), and 23517-2000- F00-TQY-PR-10051.0.TQ-R.0.01</t>
+          <t>Outstanding Process Inputs 210623 (version 1) Additional (003) (002), and 2000- F00-TQY-PR-10051.0.TQ-R.0.01</t>
         </is>
       </c>
     </row>
@@ -53372,7 +53372,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NSR email "KCGM GP - Float Cell Motors", dated 11 May 2023</t>
+          <t>Owner email "Owner GP - Float Cell Motors", dated 11 May 2023</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -53394,7 +53394,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2 T3 P5 E1 57 0- 0C 0A EL- LP UR T- I0 O0 N5_ HA L AP TG RC o Pn As Cu Km Ap Gtio En E E - 23517-ME16 TENDER - COMPLETE 20/05/22</t>
+          <t>2 T3 P5 E1 57 0- 0C 0A EL- LP UR T- I0 O0 N5_ HA L AP TG RC o Pn As Cu Km Ap Gtio En E E - ME16 TENDER - COMPLETE 20/05/22</t>
         </is>
       </c>
     </row>
@@ -53411,7 +53411,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>F reL sS u_lt1 s3x19 TSUV_Calc_Fimiston_Run 15_13x19 TSUV_ 6.5 OSS_3716 mtph_70, AVG</t>
+          <t>F reL sS u_lt1 s3x19 TSUV_Calc_FIM_Run 15_13x19 TSUV_ 6.5 OSS_3716 mtph_70, AVG</t>
         </is>
       </c>
     </row>
@@ -53428,7 +53428,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Information from the Mercury Abatement Vendor, Jan 2024 KCGM-P3-EPC-COR-161 Variation Direction No.025 Carbon regeneration kiln off-gas mercury abatement system Lochhead Carbon Reactivation Kiln (ME-17) Quotation No. 5211 (August 26, 2022) Kiln Off Gas Calc</t>
+          <t>Information from the Mercury Abatement Vendor, Jan 2024 P3-EPC-COR-161 Variation Direction No.025 Carbon regeneration kiln off-gas mercury abatement system Lochhead Carbon Reactivation Kiln (ME-17) Quotation No. 5211 (August 26, 2022) Kiln Off Gas Calc</t>
         </is>
       </c>
     </row>
@@ -53440,12 +53440,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Primero email "23517 Apron Feeder Datasheet Internal Review", dated 30 August 2023</t>
+          <t>EPC email "Apron Feeder Datasheet Internal Review", dated 30 August 2023</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Agreement with NSR to change contract SOW design factor from 120% to 110% of nominal tonnage rate.</t>
+          <t>Agreement with Owner to change contract SOW design factor from 120% to 110% of nominal tonnage rate.</t>
         </is>
       </c>
     </row>
@@ -53491,7 +53491,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KCGM GP Process Design Criteria - Reliance Information S1 Rev L, 25/01/2023</t>
+          <t>Owner GP Process Design Criteria - Reliance Information S1 Rev L, 25/01/2023</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -53508,7 +53508,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KCGM Growth Project SysCAD Model (Historical)</t>
+          <t>Growth Project SysCAD Model (Historical)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -53741,7 +53741,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -53863,7 +53863,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -53900,7 +53900,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -53937,7 +53937,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -53969,7 +53969,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -54001,7 +54001,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -54038,7 +54038,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -54075,7 +54075,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -54107,7 +54107,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -54195,7 +54195,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -54278,7 +54278,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -54330,7 +54330,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -54466,7 +54466,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -54518,7 +54518,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -54565,7 +54565,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -54612,7 +54612,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -54656,7 +54656,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -54688,7 +54688,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -54725,7 +54725,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -54757,7 +54757,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -54789,7 +54789,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -54821,7 +54821,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -54853,7 +54853,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -54966,7 +54966,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -55018,7 +55018,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -55070,7 +55070,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -55122,7 +55122,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -55159,7 +55159,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -55208,7 +55208,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -55240,7 +55240,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -55277,7 +55277,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -55309,7 +55309,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -55341,7 +55341,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -55385,7 +55385,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -55417,7 +55417,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -55449,7 +55449,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -55486,7 +55486,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -55518,7 +55518,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -55562,7 +55562,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -55594,7 +55594,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -55626,7 +55626,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -55663,7 +55663,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -55707,7 +55707,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -55739,7 +55739,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -55771,7 +55771,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -55808,7 +55808,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -55840,7 +55840,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -55862,7 +55862,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gidji Saline Transfer Dam</t>
+          <t>offsite roaster Saline Transfer Dam</t>
         </is>
       </c>
     </row>
@@ -55884,7 +55884,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -55916,7 +55916,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -55948,7 +55948,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -55985,7 +55985,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -56017,7 +56017,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -56061,7 +56061,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -56093,7 +56093,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -56130,7 +56130,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -56203,7 +56203,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -56385,7 +56385,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -56533,7 +56533,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -56585,7 +56585,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -56637,7 +56637,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -56689,7 +56689,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -56748,7 +56748,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -56800,7 +56800,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -56869,7 +56869,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -56921,7 +56921,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -57114,7 +57114,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -57173,7 +57173,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -57220,7 +57220,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -57277,7 +57277,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -57341,7 +57341,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -57393,7 +57393,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -57435,7 +57435,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -57482,7 +57482,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -57538,7 +57538,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -57570,7 +57570,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -57607,7 +57607,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -57644,7 +57644,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -57708,7 +57708,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -57752,7 +57752,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -57784,7 +57784,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -57927,7 +57927,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -57963,7 +57963,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LTD</t>
+          <t>OWNER</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr"/>
@@ -57976,7 +57976,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -58022,7 +58022,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Email Correspondence. RE 23517 - Flotation D80 Mech Requests. 250823</t>
+          <t>Email Correspondence. RE - Flotation D80 Mech Requests. 250823</t>
         </is>
       </c>
     </row>
@@ -58039,7 +58039,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reagent delivery information, provided by NSR.</t>
+          <t>Reagent delivery information, provided by Owner.</t>
         </is>
       </c>
     </row>
@@ -58053,7 +58053,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>KCGM - Northern Star (Primeo) - IsaMill Sizing - Design -19102023 - New data supplied</t>
+          <t>Owner - IsaMill Sizing - Design -19102023 - New data supplied</t>
         </is>
       </c>
     </row>
@@ -58077,7 +58077,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KCGM - Northern Star (Primeo) - IsaMill Sizing - Nominal -19102023 - New data</t>
+          <t>Owner - IsaMill Sizing - Nominal -19102023 - New data</t>
         </is>
       </c>
     </row>
@@ -58149,7 +58149,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23517-2000-F24-TQY-PR-10044.0.TQ-R.0.0164</t>
+          <t>2000-F24-TQY-PR-10044.0.TQ-R.0.0164</t>
         </is>
       </c>
     </row>
@@ -58173,7 +58173,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-085 Variation Direction No.017 Gravity Circuit Modifications</t>
+          <t>P3-EPC-COR-085 Variation Direction No.017 Gravity Circuit Modifications</t>
         </is>
       </c>
     </row>
@@ -58242,7 +58242,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>Q231115-PRI_PRIMERO_EWC 151123 issue</t>
+          <t>Q231115-PRI_EPC_EWC 151123 issue</t>
         </is>
       </c>
     </row>
@@ -58261,7 +58261,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>RE_ 23517 KCGM - Gravity Pregnant Solution Electrowinning - various emails</t>
+          <t>RE_ Gravity Pregnant Solution Electrowinning - various emails</t>
         </is>
       </c>
     </row>
@@ -58278,14 +58278,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-104 Variation Direction No.018 UFG Mill 2 Trash Screen</t>
+          <t>P3-EPC-COR-104 Variation Direction No.018 UFG Mill 2 Trash Screen</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emails with Client 21/11/23: 'RE: 23517 KCGM GP - PAX Usage/Flow</t>
+          <t>Emails with Client 21/11/23: 'RE: Owner GP - PAX Usage/Flow</t>
         </is>
       </c>
     </row>
@@ -58316,7 +58316,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dump Pocket TQ from NSR</t>
+          <t>Dump Pocket TQ from Owner</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -58350,12 +58350,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NSR Owner's Manual CAT793F KCGM</t>
+          <t>Owner Owner's Manual CAT793F Owner</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Owner's Manual CAT793F KCGM</t>
+          <t>Owner's Manual CAT793F Owner</t>
         </is>
       </c>
     </row>
@@ -58372,7 +58372,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23517-2000-F00-PFD-PR-10046.D.IFD-R.D.02</t>
+          <t>2000-F00-PFD-PR-10046.D.IFD-R.D.02</t>
         </is>
       </c>
     </row>
@@ -58423,7 +58423,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Email: RE 23517 LPG Tank, 22/05/2023</t>
+          <t>Email: RE LPG Tank, 22/05/2023</t>
         </is>
       </c>
     </row>
@@ -58447,14 +58447,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-162 Variation Direction No.026 Cyanide Tank Storage Capacity</t>
+          <t>P3-EPC-COR-162 Variation Direction No.026 Cyanide Tank Storage Capacity</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>KCGM-P3-EPC-COR-192 Variation Direction No.030 Copper Sulphate Storage</t>
+          <t>P3-EPC-COR-192 Variation Direction No.030 Copper Sulphate Storage</t>
         </is>
       </c>
     </row>
@@ -58480,7 +58480,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>RE_KCGM Growth Project - Stage 2 Vibrating Screen Changes</t>
+          <t>RE_Growth Project - Stage 2 Vibrating Screen Changes</t>
         </is>
       </c>
     </row>
@@ -58497,7 +58497,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6454-Primero-KCGM-Carbon Scout-220426, 22/04/22</t>
+          <t>6454-EPC-Carbon Scout-220426, 22/04/22</t>
         </is>
       </c>
     </row>
@@ -58531,7 +58531,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P28337_Northern Star_Primero Group_KCGM Growth (Aus) REV 2</t>
+          <t>P28337_Owner_EPC_Growth (Aus) REV 2</t>
         </is>
       </c>
     </row>
@@ -58548,7 +58548,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>23517-2000-F00-TQY-PR-10206.0.TQ-R.0.0270</t>
+          <t>2000-F00-TQY-PR-10206.0.TQ-R.0.0270</t>
         </is>
       </c>
     </row>
@@ -58582,7 +58582,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>23517-2000-F00-DCR-PR-10001.0.IFD-R.0.02</t>
+          <t>2000-F00-DCR-PR-10001.0.IFD-R.0.02</t>
         </is>
       </c>
     </row>
@@ -58599,7 +58599,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>23517-CAL-PR-003 S2 Oxygen Consumption Calculations</t>
+          <t>CAL-PR-003 S2 Oxygen Consumption Calculations</t>
         </is>
       </c>
     </row>
@@ -58646,7 +58646,7 @@
     <row r="57">
       <c r="C57" t="inlineStr">
         <is>
-          <t>DRA Process Design Criteria - KCGM Growth Project ECS. 25/01/2022</t>
+          <t>Engineer Process Design Criteria - Growth Project ECS. 25/01/2022</t>
         </is>
       </c>
     </row>
@@ -58672,7 +58672,7 @@
     <row r="60">
       <c r="C60" t="inlineStr">
         <is>
-          <t>DRA Mass Balance - KCGM Growth Project ECS. 25/01/2022</t>
+          <t>Engineer Mass Balance - Growth Project ECS. 25/01/2022</t>
         </is>
       </c>
     </row>
@@ -58708,7 +58708,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KCGM - Growth Project - Process Design Criteria Rev F. 16/03/2022</t>
+          <t>Growth Project - Process Design Criteria Rev F. 16/03/2022</t>
         </is>
       </c>
     </row>
@@ -58720,7 +58720,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.5.1 - KCGM Process Design Criteria - VEP Phase _H, 19/08/2022</t>
+          <t>4.5.1 - Owner Process Design Criteria - VEP Phase _H, 19/08/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -58732,7 +58732,7 @@
     <row r="65">
       <c r="C65" t="inlineStr">
         <is>
-          <t>Confirmation from NSR that currently proposed screen sizes for Carbon Safety Screens</t>
+          <t>Confirmation from Owner that currently proposed screen sizes for Carbon Safety Screens</t>
         </is>
       </c>
     </row>
@@ -58909,7 +58909,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LTD</t>
+          <t>OWNER</t>
         </is>
       </c>
     </row>
@@ -58921,7 +58921,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -59265,7 +59265,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -59380,7 +59380,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -59437,7 +59437,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -59513,7 +59513,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -59765,7 +59765,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -60054,7 +60054,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -60162,7 +60162,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -60194,7 +60194,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -60226,7 +60226,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -60258,7 +60258,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -60290,7 +60290,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -60329,7 +60329,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -60371,7 +60371,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -60408,7 +60408,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -60464,7 +60464,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -60501,7 +60501,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -60538,7 +60538,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -60582,7 +60582,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -60614,7 +60614,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -60646,7 +60646,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -60683,7 +60683,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -60720,7 +60720,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -60757,7 +60757,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -60789,7 +60789,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -60843,7 +60843,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -60880,7 +60880,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -60917,7 +60917,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -60954,7 +60954,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -61018,7 +61018,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -61028,7 +61028,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Achievable grade back calculated by Primero (Source 32)</t>
+          <t>Achievable grade back calculated by EPC (Source 32)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -61075,7 +61075,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -61085,7 +61085,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Achievable grade back calculated by Primero (Source 32)</t>
+          <t>Achievable grade back calculated by EPC (Source 32)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -61132,7 +61132,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -61142,7 +61142,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Blue data is from NSR Ref 23</t>
+          <t>Blue data is from Owner Ref 23</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -61189,7 +61189,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -61199,7 +61199,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Blue data is from NSR Ref 23</t>
+          <t>Blue data is from Owner Ref 23</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -61248,7 +61248,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -61290,7 +61290,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -61332,7 +61332,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -61342,7 +61342,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Blue data is from NSR Ref 23</t>
+          <t>Blue data is from Owner Ref 23</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -61379,7 +61379,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -61389,7 +61389,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Blue data is from NSR Ref 23</t>
+          <t>Blue data is from Owner Ref 23</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -61490,7 +61490,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -61547,7 +61547,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -61604,7 +61604,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -61661,7 +61661,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -61718,7 +61718,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -61775,7 +61775,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -61832,7 +61832,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -61889,7 +61889,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -61946,7 +61946,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -62003,7 +62003,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -62168,7 +62168,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -62220,7 +62220,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -62348,7 +62348,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -62400,7 +62400,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -62464,7 +62464,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -62516,7 +62516,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -62568,7 +62568,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -62620,7 +62620,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -62684,7 +62684,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Northern Star, Vendor</t>
+          <t>Owner, Vendor</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -62743,7 +62743,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -62790,7 +62790,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -62842,7 +62842,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -62899,7 +62899,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -62956,7 +62956,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -63025,7 +63025,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -63035,7 +63035,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -63082,7 +63082,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -63092,7 +63092,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -63196,7 +63196,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -63544,7 +63544,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -63642,7 +63642,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -63793,7 +63793,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -63845,7 +63845,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -64023,7 +64023,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -64203,7 +64203,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -64250,7 +64250,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -64344,7 +64344,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -64408,7 +64408,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Primero, Northern Star</t>
+          <t>EPC, Owner</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -64460,7 +64460,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -64618,7 +64618,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -64665,7 +64665,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -64811,7 +64811,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -64887,7 +64887,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -65008,7 +65008,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -65072,7 +65072,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Northern Star, Vendor</t>
+          <t>Owner, Vendor</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -65129,7 +65129,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -65166,7 +65166,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -65203,7 +65203,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -65240,7 +65240,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -65277,7 +65277,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -65381,7 +65381,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -65428,7 +65428,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -65465,7 +65465,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -65529,7 +65529,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -65539,7 +65539,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -65591,7 +65591,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -65601,7 +65601,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -65653,7 +65653,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -65663,7 +65663,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -65715,7 +65715,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -65772,7 +65772,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -65829,7 +65829,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -65881,7 +65881,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -65938,7 +65938,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -66000,7 +66000,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -66057,7 +66057,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -66166,7 +66166,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -66213,7 +66213,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -66265,7 +66265,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -66317,7 +66317,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -66374,7 +66374,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -66478,7 +66478,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -66530,7 +66530,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -66587,7 +66587,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -66639,7 +66639,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -66676,7 +66676,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -66735,7 +66735,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -66943,7 +66943,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -67161,7 +67161,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -67213,7 +67213,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -67272,7 +67272,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -67282,7 +67282,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -67329,7 +67329,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -67339,7 +67339,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -67386,7 +67386,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -67396,7 +67396,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -67443,7 +67443,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -67495,7 +67495,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -67547,7 +67547,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -67599,7 +67599,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -67750,7 +67750,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -67797,7 +67797,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -67948,7 +67948,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -68052,7 +68052,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -68104,7 +68104,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -68156,7 +68156,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -68220,7 +68220,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -68230,7 +68230,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -68277,7 +68277,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -68287,7 +68287,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -68334,7 +68334,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -68344,7 +68344,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -68396,7 +68396,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -68453,7 +68453,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -68505,7 +68505,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -68557,7 +68557,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -68653,7 +68653,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -68690,7 +68690,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -68722,7 +68722,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -68818,7 +68818,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -68887,7 +68887,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star, Primero</t>
+          <t>Owner, EPC</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -69033,7 +69033,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -69092,7 +69092,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -69149,7 +69149,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -69206,7 +69206,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -69270,7 +69270,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -69339,7 +69339,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -69391,7 +69391,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -69401,7 +69401,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>OMC Modelling</t>
+          <t>Consultant Modelling</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -69448,7 +69448,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -69458,7 +69458,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>OMC Modelling</t>
+          <t>Consultant Modelling</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -69505,7 +69505,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -69515,7 +69515,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>OMC Modelling</t>
+          <t>Consultant Modelling</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -69562,7 +69562,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -69614,7 +69614,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -69661,7 +69661,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -70286,7 +70286,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -70572,7 +70572,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -70688,7 +70688,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -71123,7 +71123,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -71207,7 +71207,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -71254,7 +71254,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -71598,7 +71598,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -72023,7 +72023,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -72070,7 +72070,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -72226,7 +72226,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -72330,7 +72330,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -72429,7 +72429,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -72594,7 +72594,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -72747,7 +72747,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -72940,7 +72940,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -73133,7 +73133,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -73185,7 +73185,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -73237,7 +73237,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -73331,7 +73331,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>requested by NSR in source 16</t>
+          <t>requested by Owner in source 16</t>
         </is>
       </c>
     </row>
@@ -73472,7 +73472,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -73519,7 +73519,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -73578,7 +73578,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -73625,7 +73625,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -73677,7 +73677,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -73833,7 +73833,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Primero, Vendor</t>
+          <t>EPC, Vendor</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -74308,7 +74308,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -74476,7 +74476,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -74547,7 +74547,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -74594,7 +74594,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -74641,7 +74641,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -74745,7 +74745,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Required to complete 2 batches per day as per NSR Source 72</t>
+          <t>Required to complete 2 batches per day as per Owner Source 72</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -74938,7 +74938,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -74995,7 +74995,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -75220,7 +75220,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -75272,7 +75272,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -75329,7 +75329,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -75517,7 +75517,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -75574,7 +75574,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -75732,7 +75732,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -75784,7 +75784,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -75836,7 +75836,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -75888,7 +75888,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -75945,7 +75945,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Two electrowinning runs as required per day as per NSR Source</t>
+          <t>Two electrowinning runs as required per day as per Owner Source</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -75999,7 +75999,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -76510,7 +76510,7 @@
     <row r="6">
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIMISTON</t>
+          <t>FIM</t>
         </is>
       </c>
     </row>
@@ -76662,7 +76662,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -76714,7 +76714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -76768,7 +76768,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -76815,7 +76815,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -76862,7 +76862,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -76909,7 +76909,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -76956,7 +76956,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -77003,7 +77003,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -77087,7 +77087,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
     </row>
@@ -77124,7 +77124,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -77349,7 +77349,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -77443,7 +77443,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -77537,7 +77537,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -77589,7 +77589,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -77683,7 +77683,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -77772,7 +77772,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -77965,7 +77965,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -78059,7 +78059,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -78111,7 +78111,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -78205,7 +78205,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -78294,7 +78294,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -78571,7 +78571,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -78618,7 +78618,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -78665,7 +78665,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -78717,7 +78717,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -78811,7 +78811,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -78924,7 +78924,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -78976,7 +78976,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -79003,7 +79003,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
     </row>
@@ -79040,7 +79040,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -79218,7 +79218,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -79307,7 +79307,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -79401,7 +79401,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -79453,7 +79453,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -79547,7 +79547,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -79636,7 +79636,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -79688,7 +79688,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -79965,7 +79965,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -80012,7 +80012,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -80059,7 +80059,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -80111,7 +80111,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -80205,7 +80205,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -80318,7 +80318,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -80370,7 +80370,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -80434,7 +80434,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>NSR Supplied</t>
+          <t>Owner Supplied</t>
         </is>
       </c>
     </row>
@@ -80471,7 +80471,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -80949,7 +80949,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -81043,7 +81043,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Northern Star</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -81273,7 +81273,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Primero</t>
+          <t>EPC</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
